--- a/process_mining_assignment/process_mining_report_Order_Process_Log_100_Cases.xlsx
+++ b/process_mining_assignment/process_mining_report_Order_Process_Log_100_Cases.xlsx
@@ -14405,7 +14405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Input: {Check inventory, Manual review}  →  Output: {Approve order}</t>
+          <t>Input: {Check inventory}  →  Output: {Approve order}</t>
         </is>
       </c>
     </row>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Input: {Pack order}  →  Output: {Ship order}</t>
+          <t>Input: {Manual review}  →  Output: {Approve order}</t>
         </is>
       </c>
     </row>
@@ -14516,29 +14516,53 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Input: {Receive order}  →  Output: {Cancel order, Check inventory, Manual review}</t>
+          <t>Input: {Pack order}  →  Output: {Ship order}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p_start (source)</t>
+          <t>Place p5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>→ ['Receive order']</t>
+          <t>Input: {Receive order}  →  Output: {Cancel order, Check inventory}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Place p6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Input: {Receive order}  →  Output: {Cancel order, Manual review}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>p_start (source)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>→ ['Receive order']</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>p_end (sink)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>['Cancel order', 'Ship order'] →</t>
         </is>
